--- a/dataset_t6_grouped/results2/G1/G1_T6020_W0056F0001T0006Z000C1N9_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T6020_W0056F0001T0006Z000C1N9_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>27.26723970465494</v>
+        <v>4.430926452006428</v>
       </c>
       <c r="D2" t="n">
-        <v>18.58123638725401</v>
+        <v>3.019450912928777</v>
       </c>
       <c r="E2" t="n">
-        <v>6.180431876606363</v>
+        <v>1.004320179948534</v>
       </c>
       <c r="F2" t="n">
-        <v>5.087626824818009</v>
+        <v>0.8267393590329264</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>13.57202169593916</v>
+        <v>2.205453525590113</v>
       </c>
       <c r="D3" t="n">
-        <v>12.58917335621595</v>
+        <v>2.045740670385093</v>
       </c>
       <c r="E3" t="n">
-        <v>6.180431876606363</v>
+        <v>1.004320179948534</v>
       </c>
       <c r="F3" t="n">
-        <v>5.087626824818009</v>
+        <v>0.8267393590329264</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>26.0071681352038</v>
+        <v>4.226164821970618</v>
       </c>
       <c r="D4" t="n">
-        <v>6.122163835007665</v>
+        <v>0.9948516231887456</v>
       </c>
       <c r="E4" t="n">
-        <v>6.180431876606363</v>
+        <v>1.004320179948534</v>
       </c>
       <c r="F4" t="n">
-        <v>5.087626824818009</v>
+        <v>0.8267393590329264</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
